--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,48 +800,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3000042</v>
+        <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>92806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>barrskog 500 m OSO om KARLSHED, Vg</t>
+          <t>Galgberget, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362981</v>
+        <v>362935</v>
       </c>
       <c r="R3" t="n">
-        <v>6373922</v>
+        <v>6373987</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1998-07-10</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1998-07-10</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,28 +899,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Jerker Nordh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kenneth Hansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Jerker Nordh</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3000042</t>
+          <t>https://artportalen.se/Sighting/137160901</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3051425</v>
+        <v>3000042</v>
       </c>
       <c r="B4" t="n">
         <v>99118</v>
@@ -934,34 +944,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karlshedskogen, Vg</t>
+          <t>barrskog 500 m OSO om KARLSHED, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>362858</v>
+        <v>362981</v>
       </c>
       <c r="R4" t="n">
-        <v>6373756</v>
+        <v>6373922</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-08-20</t>
+          <t>1998-07-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-08-20</t>
+          <t>1998-07-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,33 +997,32 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>torr barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Kenneth Hansson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Kenneth Hansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3051425</t>
+          <t>https://artportalen.se/Sighting/3000042</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17212482</v>
+        <v>3051425</v>
       </c>
       <c r="B5" t="n">
         <v>99118</v>
@@ -1057,7 +1052,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1070,20 +1065,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Karlhedskogen, Vg</t>
+          <t>Karlshedskogen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363008</v>
+        <v>362858</v>
       </c>
       <c r="R5" t="n">
-        <v>6373805</v>
+        <v>6373756</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,19 +1099,14 @@
           <t>Örby</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>OV-Mar-0031</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-08-17</t>
+          <t>2011-08-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-08-17</t>
+          <t>2011-08-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,14 +1118,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>torr barrskog, sydvänd</t>
+          <t>torr barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1150,12 +1134,144 @@
           <t>Kenneth Hansson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3051425</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17212482</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Karlhedskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>363008</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6373805</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Örby</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>OV-Mar-0031</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-08-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>torr barrskog, sydvänd</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kenneth Hansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kenneth Hansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/17212482</t>
         </is>
@@ -1167,6 +1283,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137160901</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
